--- a/HeroInfo.xlsx
+++ b/HeroInfo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\All\CharacterInfo-API\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA93DA94-A3FE-44CA-ABC2-09E458B4F917}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9F02D80-2096-4146-B098-F913DF0435CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{FD8D03F1-1FE8-46BA-AC23-ADF5BD740510}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7680" uniqueCount="2494">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7680" uniqueCount="2495">
   <si>
     <t>HeroName</t>
   </si>
@@ -7603,6 +7603,9 @@
   </si>
   <si>
     <t>https://static.wikia.nocookie.net/mobile-legends/images/5/5c/Black_Dragon_Form.png</t>
+  </si>
+  <si>
+    <t>null</t>
   </si>
 </sst>
 </file>
@@ -16107,34 +16110,34 @@
         <v>2314</v>
       </c>
       <c r="T2" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U2" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V2" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W2" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X2" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y2" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z2" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA2" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB2" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC2" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD2" s="7" t="s">
         <v>235</v>
@@ -16259,34 +16262,34 @@
         <v>2315</v>
       </c>
       <c r="T3" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U3" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V3" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W3" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X3" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y3" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z3" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA3" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB3" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC3" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD3" s="8" t="s">
         <v>232</v>
@@ -16411,34 +16414,34 @@
         <v>2316</v>
       </c>
       <c r="T4" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U4" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V4" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W4" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X4" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y4" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z4" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA4" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB4" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC4" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD4" s="9" t="s">
         <v>268</v>
@@ -16563,34 +16566,34 @@
         <v>2317</v>
       </c>
       <c r="T5" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U5" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V5" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W5" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X5" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y5" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z5" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA5" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB5" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC5" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD5" s="9" t="s">
         <v>233</v>
@@ -16715,34 +16718,34 @@
         <v>2318</v>
       </c>
       <c r="T6" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U6" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V6" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W6" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X6" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y6" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z6" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA6" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB6" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC6" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD6" s="9" t="s">
         <v>247</v>
@@ -16867,34 +16870,34 @@
         <v>2319</v>
       </c>
       <c r="T7" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U7" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V7" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W7" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X7" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y7" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z7" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA7" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB7" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC7" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD7" s="9" t="s">
         <v>235</v>
@@ -17019,34 +17022,34 @@
         <v>2320</v>
       </c>
       <c r="T8" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U8" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V8" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W8" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X8" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y8" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z8" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA8" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB8" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC8" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD8" s="8" t="s">
         <v>232</v>
@@ -17171,34 +17174,34 @@
         <v>2321</v>
       </c>
       <c r="T9" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U9" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V9" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W9" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X9" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y9" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z9" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA9" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB9" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC9" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD9" s="9" t="s">
         <v>233</v>
@@ -17323,34 +17326,34 @@
         <v>2322</v>
       </c>
       <c r="T10" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U10" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V10" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W10" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X10" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y10" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z10" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA10" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB10" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC10" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD10" s="9" t="s">
         <v>247</v>
@@ -17475,34 +17478,34 @@
         <v>2323</v>
       </c>
       <c r="T11" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U11" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V11" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W11" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X11" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y11" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z11" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA11" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB11" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC11" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD11" s="9" t="s">
         <v>269</v>
@@ -17627,34 +17630,34 @@
         <v>2324</v>
       </c>
       <c r="T12" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U12" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V12" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W12" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X12" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y12" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z12" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA12" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB12" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC12" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD12" s="9" t="s">
         <v>247</v>
@@ -17779,34 +17782,34 @@
         <v>2325</v>
       </c>
       <c r="T13" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U13" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V13" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W13" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X13" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y13" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z13" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA13" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB13" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC13" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD13" s="7" t="s">
         <v>239</v>
@@ -17931,34 +17934,34 @@
         <v>2326</v>
       </c>
       <c r="T14" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U14" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V14" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W14" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X14" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y14" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z14" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA14" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB14" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC14" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD14" s="9" t="s">
         <v>239</v>
@@ -18083,34 +18086,34 @@
         <v>2327</v>
       </c>
       <c r="T15" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U15" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V15" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W15" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X15" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y15" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z15" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA15" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB15" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC15" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD15" s="9" t="s">
         <v>269</v>
@@ -18235,34 +18238,34 @@
         <v>2328</v>
       </c>
       <c r="T16" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U16" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V16" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W16" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X16" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y16" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z16" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA16" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB16" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC16" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD16" s="9" t="s">
         <v>235</v>
@@ -18387,34 +18390,34 @@
         <v>2329</v>
       </c>
       <c r="T17" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U17" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V17" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W17" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X17" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y17" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z17" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA17" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB17" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC17" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD17" s="9" t="s">
         <v>258</v>
@@ -18539,34 +18542,34 @@
         <v>2330</v>
       </c>
       <c r="T18" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U18" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V18" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W18" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X18" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y18" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z18" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA18" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB18" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC18" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD18" s="9" t="s">
         <v>258</v>
@@ -18691,34 +18694,34 @@
         <v>2331</v>
       </c>
       <c r="T19" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U19" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V19" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W19" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X19" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y19" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z19" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA19" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB19" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC19" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD19" s="9" t="s">
         <v>232</v>
@@ -18843,34 +18846,34 @@
         <v>2332</v>
       </c>
       <c r="T20" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U20" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V20" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W20" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X20" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y20" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z20" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA20" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB20" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC20" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD20" s="9" t="s">
         <v>268</v>
@@ -18995,34 +18998,34 @@
         <v>2333</v>
       </c>
       <c r="T21" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U21" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V21" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W21" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X21" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y21" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z21" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA21" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB21" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC21" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD21" s="8" t="s">
         <v>247</v>
@@ -19147,34 +19150,34 @@
         <v>2334</v>
       </c>
       <c r="T22" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U22" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V22" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W22" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X22" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y22" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z22" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA22" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB22" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC22" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD22" s="5" t="s">
         <v>239</v>
@@ -19299,34 +19302,34 @@
         <v>2335</v>
       </c>
       <c r="T23" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U23" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V23" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W23" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X23" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y23" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z23" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA23" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB23" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC23" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD23" s="9" t="s">
         <v>248</v>
@@ -19451,34 +19454,34 @@
         <v>2336</v>
       </c>
       <c r="T24" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U24" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V24" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W24" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X24" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y24" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z24" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA24" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB24" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC24" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD24" s="8" t="s">
         <v>268</v>
@@ -19603,34 +19606,34 @@
         <v>2337</v>
       </c>
       <c r="T25" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U25" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V25" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W25" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X25" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y25" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z25" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA25" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB25" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC25" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD25" s="7" t="s">
         <v>239</v>
@@ -19755,34 +19758,34 @@
         <v>2338</v>
       </c>
       <c r="T26" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U26" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V26" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W26" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X26" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y26" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z26" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA26" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB26" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC26" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD26" s="7" t="s">
         <v>239</v>
@@ -19907,34 +19910,34 @@
         <v>2339</v>
       </c>
       <c r="T27" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U27" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V27" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W27" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X27" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y27" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z27" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA27" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB27" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC27" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD27" s="5" t="s">
         <v>269</v>
@@ -20059,34 +20062,34 @@
         <v>2340</v>
       </c>
       <c r="T28" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U28" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V28" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W28" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X28" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y28" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z28" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA28" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB28" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC28" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD28" s="9" t="s">
         <v>235</v>
@@ -20211,34 +20214,34 @@
         <v>2341</v>
       </c>
       <c r="T29" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U29" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V29" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W29" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X29" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y29" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z29" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA29" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB29" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC29" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD29" s="9" t="s">
         <v>235</v>
@@ -20363,34 +20366,34 @@
         <v>2342</v>
       </c>
       <c r="T30" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U30" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V30" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W30" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X30" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y30" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z30" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA30" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB30" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC30" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD30" s="9" t="s">
         <v>232</v>
@@ -20515,34 +20518,34 @@
         <v>2343</v>
       </c>
       <c r="T31" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U31" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V31" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W31" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X31" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y31" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z31" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA31" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB31" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC31" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD31" s="9" t="s">
         <v>232</v>
@@ -20667,34 +20670,34 @@
         <v>2344</v>
       </c>
       <c r="T32" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U32" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V32" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W32" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X32" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y32" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z32" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA32" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB32" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC32" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD32" s="7" t="s">
         <v>232</v>
@@ -20819,34 +20822,34 @@
         <v>2345</v>
       </c>
       <c r="T33" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U33" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V33" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W33" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X33" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y33" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z33" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA33" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB33" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC33" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD33" s="8" t="s">
         <v>239</v>
@@ -20971,34 +20974,34 @@
         <v>2346</v>
       </c>
       <c r="T34" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U34" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V34" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W34" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X34" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y34" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z34" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA34" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB34" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC34" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD34" s="9" t="s">
         <v>235</v>
@@ -21123,34 +21126,34 @@
         <v>2347</v>
       </c>
       <c r="T35" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U35" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V35" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W35" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X35" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y35" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z35" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA35" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB35" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC35" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD35" s="9" t="s">
         <v>233</v>
@@ -21275,34 +21278,34 @@
         <v>2348</v>
       </c>
       <c r="T36" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U36" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V36" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W36" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X36" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y36" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z36" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA36" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB36" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC36" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD36" s="7" t="s">
         <v>268</v>
@@ -21427,34 +21430,34 @@
         <v>2349</v>
       </c>
       <c r="T37" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U37" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V37" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W37" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X37" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y37" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z37" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA37" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB37" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC37" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD37" s="8" t="s">
         <v>233</v>
@@ -21579,34 +21582,34 @@
         <v>2350</v>
       </c>
       <c r="T38" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U38" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V38" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W38" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X38" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y38" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z38" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA38" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB38" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC38" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD38" s="7" t="s">
         <v>234</v>
@@ -21731,34 +21734,34 @@
         <v>2351</v>
       </c>
       <c r="T39" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U39" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V39" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W39" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X39" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y39" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z39" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA39" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB39" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC39" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD39" s="8" t="s">
         <v>247</v>
@@ -21883,34 +21886,34 @@
         <v>2352</v>
       </c>
       <c r="T40" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U40" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V40" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W40" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X40" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y40" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z40" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA40" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB40" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC40" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD40" s="8" t="s">
         <v>239</v>
@@ -22035,34 +22038,34 @@
         <v>2353</v>
       </c>
       <c r="T41" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U41" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V41" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W41" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X41" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y41" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z41" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA41" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB41" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC41" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD41" s="8" t="s">
         <v>247</v>
@@ -22187,34 +22190,34 @@
         <v>2354</v>
       </c>
       <c r="T42" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U42" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V42" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W42" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X42" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y42" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z42" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA42" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB42" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC42" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD42" s="9" t="s">
         <v>269</v>
@@ -22345,28 +22348,28 @@
         <v>2486</v>
       </c>
       <c r="V43" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W43" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X43" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y43" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z43" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA43" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB43" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC43" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD43" s="9" t="s">
         <v>269</v>
@@ -22491,34 +22494,34 @@
         <v>2356</v>
       </c>
       <c r="T44" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U44" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V44" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W44" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X44" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y44" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z44" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA44" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB44" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC44" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD44" s="9" t="s">
         <v>247</v>
@@ -22643,34 +22646,34 @@
         <v>2357</v>
       </c>
       <c r="T45" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U45" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V45" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W45" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X45" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y45" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z45" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA45" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB45" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC45" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD45" s="9" t="s">
         <v>268</v>
@@ -22795,34 +22798,34 @@
         <v>2358</v>
       </c>
       <c r="T46" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U46" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V46" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W46" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X46" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y46" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z46" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA46" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB46" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC46" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD46" s="9" t="s">
         <v>258</v>
@@ -22947,34 +22950,34 @@
         <v>2359</v>
       </c>
       <c r="T47" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U47" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V47" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W47" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X47" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y47" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z47" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA47" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB47" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC47" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD47" s="7" t="s">
         <v>234</v>
@@ -23099,34 +23102,34 @@
         <v>2360</v>
       </c>
       <c r="T48" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U48" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V48" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W48" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X48" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y48" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z48" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA48" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB48" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC48" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD48" s="9" t="s">
         <v>232</v>
@@ -23251,34 +23254,34 @@
         <v>2361</v>
       </c>
       <c r="T49" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U49" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V49" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W49" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X49" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y49" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z49" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA49" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB49" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC49" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD49" s="9" t="s">
         <v>268</v>
@@ -23403,34 +23406,34 @@
         <v>2362</v>
       </c>
       <c r="T50" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U50" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V50" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W50" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X50" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y50" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z50" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA50" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB50" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC50" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD50" s="9" t="s">
         <v>239</v>
@@ -23555,34 +23558,34 @@
         <v>2363</v>
       </c>
       <c r="T51" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U51" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V51" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W51" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X51" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y51" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z51" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA51" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB51" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC51" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD51" s="8" t="s">
         <v>232</v>
@@ -23707,34 +23710,34 @@
         <v>2364</v>
       </c>
       <c r="T52" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U52" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V52" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W52" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X52" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y52" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z52" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA52" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB52" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC52" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD52" s="9" t="s">
         <v>248</v>
@@ -23859,34 +23862,34 @@
         <v>2365</v>
       </c>
       <c r="T53" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U53" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V53" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W53" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X53" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y53" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z53" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA53" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB53" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC53" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD53" s="8" t="s">
         <v>233</v>
@@ -24011,34 +24014,34 @@
         <v>2366</v>
       </c>
       <c r="T54" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U54" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V54" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W54" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X54" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y54" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z54" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA54" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB54" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC54" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD54" s="7" t="s">
         <v>239</v>
@@ -24163,34 +24166,34 @@
         <v>2367</v>
       </c>
       <c r="T55" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U55" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V55" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W55" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X55" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y55" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z55" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA55" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB55" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC55" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD55" s="8" t="s">
         <v>232</v>
@@ -24315,34 +24318,34 @@
         <v>2368</v>
       </c>
       <c r="T56" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U56" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V56" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W56" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X56" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y56" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z56" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA56" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB56" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC56" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD56" s="8" t="s">
         <v>239</v>
@@ -24467,34 +24470,34 @@
         <v>2369</v>
       </c>
       <c r="T57" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U57" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V57" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W57" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X57" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y57" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z57" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA57" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB57" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC57" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD57" s="8" t="s">
         <v>232</v>
@@ -24619,34 +24622,34 @@
         <v>2370</v>
       </c>
       <c r="T58" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U58" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V58" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W58" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X58" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y58" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z58" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA58" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB58" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC58" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD58" s="9" t="s">
         <v>268</v>
@@ -24771,34 +24774,34 @@
         <v>2371</v>
       </c>
       <c r="T59" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U59" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V59" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W59" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X59" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y59" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z59" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA59" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB59" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC59" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD59" s="9" t="s">
         <v>258</v>
@@ -24923,34 +24926,34 @@
         <v>2372</v>
       </c>
       <c r="T60" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U60" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V60" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W60" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X60" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y60" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z60" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA60" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB60" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC60" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD60" s="9" t="s">
         <v>234</v>
@@ -25075,34 +25078,34 @@
         <v>2373</v>
       </c>
       <c r="T61" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U61" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V61" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W61" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X61" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y61" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z61" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA61" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB61" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC61" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD61" s="9" t="s">
         <v>232</v>
@@ -25227,34 +25230,34 @@
         <v>2374</v>
       </c>
       <c r="T62" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U62" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V62" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W62" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X62" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y62" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z62" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA62" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB62" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC62" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD62" s="9" t="s">
         <v>247</v>
@@ -25379,34 +25382,34 @@
         <v>2375</v>
       </c>
       <c r="T63" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U63" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V63" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W63" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X63" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y63" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z63" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA63" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB63" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC63" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD63" s="9" t="s">
         <v>269</v>
@@ -25531,34 +25534,34 @@
         <v>2376</v>
       </c>
       <c r="T64" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U64" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V64" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W64" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X64" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y64" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z64" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA64" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB64" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC64" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD64" s="8" t="s">
         <v>232</v>
@@ -25683,34 +25686,34 @@
         <v>2377</v>
       </c>
       <c r="T65" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U65" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V65" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W65" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X65" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y65" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z65" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA65" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB65" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC65" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD65" s="9" t="s">
         <v>247</v>
@@ -25835,34 +25838,34 @@
         <v>2378</v>
       </c>
       <c r="T66" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U66" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V66" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W66" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X66" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y66" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z66" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA66" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB66" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC66" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD66" s="7" t="s">
         <v>239</v>
@@ -25987,34 +25990,34 @@
         <v>2379</v>
       </c>
       <c r="T67" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U67" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V67" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W67" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X67" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y67" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z67" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA67" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB67" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC67" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD67" s="7" t="s">
         <v>232</v>
@@ -26139,34 +26142,34 @@
         <v>2380</v>
       </c>
       <c r="T68" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U68" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V68" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W68" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X68" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y68" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z68" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA68" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB68" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC68" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD68" s="8" t="s">
         <v>232</v>
@@ -26291,34 +26294,34 @@
         <v>2381</v>
       </c>
       <c r="T69" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U69" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V69" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W69" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X69" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y69" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z69" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA69" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB69" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC69" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD69" s="5" t="s">
         <v>269</v>
@@ -26443,34 +26446,34 @@
         <v>2382</v>
       </c>
       <c r="T70" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U70" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V70" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W70" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X70" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y70" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z70" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA70" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB70" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC70" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD70" s="8" t="s">
         <v>235</v>
@@ -26595,34 +26598,34 @@
         <v>2383</v>
       </c>
       <c r="T71" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U71" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V71" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W71" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X71" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y71" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z71" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA71" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB71" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC71" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD71" s="9" t="s">
         <v>232</v>
@@ -26747,34 +26750,34 @@
         <v>2384</v>
       </c>
       <c r="T72" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U72" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V72" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W72" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X72" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y72" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z72" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA72" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB72" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC72" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD72" s="9" t="s">
         <v>269</v>
@@ -26899,34 +26902,34 @@
         <v>2385</v>
       </c>
       <c r="T73" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U73" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V73" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W73" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X73" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y73" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z73" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA73" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB73" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC73" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD73" s="9" t="s">
         <v>268</v>
@@ -27051,34 +27054,34 @@
         <v>2386</v>
       </c>
       <c r="T74" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U74" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V74" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W74" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X74" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y74" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z74" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA74" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB74" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC74" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD74" s="9" t="s">
         <v>248</v>
@@ -27203,34 +27206,34 @@
         <v>2387</v>
       </c>
       <c r="T75" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U75" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V75" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W75" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X75" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y75" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z75" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA75" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB75" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC75" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD75" s="8" t="s">
         <v>239</v>
@@ -27355,34 +27358,34 @@
         <v>2388</v>
       </c>
       <c r="T76" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U76" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V76" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W76" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X76" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y76" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z76" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA76" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB76" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC76" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD76" s="9" t="s">
         <v>269</v>
@@ -27507,34 +27510,34 @@
         <v>2389</v>
       </c>
       <c r="T77" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U77" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V77" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W77" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X77" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y77" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z77" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA77" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB77" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC77" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD77" s="9" t="s">
         <v>234</v>
@@ -27659,34 +27662,34 @@
         <v>2390</v>
       </c>
       <c r="T78" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U78" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V78" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W78" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X78" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y78" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z78" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA78" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB78" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC78" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD78" s="9" t="s">
         <v>233</v>
@@ -27811,34 +27814,34 @@
         <v>2391</v>
       </c>
       <c r="T79" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U79" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V79" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W79" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X79" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y79" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z79" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA79" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB79" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC79" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD79" s="9" t="s">
         <v>234</v>
@@ -27963,34 +27966,34 @@
         <v>2392</v>
       </c>
       <c r="T80" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U80" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V80" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W80" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X80" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y80" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z80" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA80" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB80" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC80" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD80" s="8" t="s">
         <v>235</v>
@@ -28115,34 +28118,34 @@
         <v>2393</v>
       </c>
       <c r="T81" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U81" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V81" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W81" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X81" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y81" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z81" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA81" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB81" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC81" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD81" s="8" t="s">
         <v>258</v>
@@ -28267,34 +28270,34 @@
         <v>2394</v>
       </c>
       <c r="T82" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U82" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V82" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W82" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X82" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y82" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z82" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA82" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB82" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC82" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD82" s="5" t="s">
         <v>269</v>
@@ -28425,28 +28428,28 @@
         <v>2475</v>
       </c>
       <c r="V83" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W83" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X83" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y83" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z83" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA83" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB83" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC83" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD83" s="7">
         <v>3</v>
@@ -28571,34 +28574,34 @@
         <v>2396</v>
       </c>
       <c r="T84" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U84" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V84" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W84" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X84" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y84" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z84" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA84" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB84" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC84" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD84" s="7">
         <v>2</v>
@@ -28723,34 +28726,34 @@
         <v>2397</v>
       </c>
       <c r="T85" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U85" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V85" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W85" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X85" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y85" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z85" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA85" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB85" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC85" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD85" s="7">
         <v>5</v>
@@ -28875,34 +28878,34 @@
         <v>2398</v>
       </c>
       <c r="T86" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U86" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V86" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W86" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X86" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y86" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z86" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA86" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB86" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC86" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD86" s="9" t="s">
         <v>247</v>
@@ -29027,34 +29030,34 @@
         <v>2399</v>
       </c>
       <c r="T87" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U87" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V87" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W87" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X87" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y87" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z87" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA87" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB87" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC87" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD87" s="9" t="s">
         <v>235</v>
@@ -29179,34 +29182,34 @@
         <v>2400</v>
       </c>
       <c r="T88" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U88" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V88" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W88" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X88" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y88" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z88" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA88" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB88" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC88" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD88" s="9" t="s">
         <v>269</v>
@@ -29331,34 +29334,34 @@
         <v>2401</v>
       </c>
       <c r="T89" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U89" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V89" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W89" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X89" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y89" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z89" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA89" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB89" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC89" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD89" s="9" t="s">
         <v>248</v>
@@ -29483,34 +29486,34 @@
         <v>2402</v>
       </c>
       <c r="T90" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U90" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V90" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W90" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X90" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y90" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z90" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA90" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB90" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC90" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD90" s="9" t="s">
         <v>258</v>
@@ -29635,34 +29638,34 @@
         <v>2403</v>
       </c>
       <c r="T91" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U91" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V91" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W91" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X91" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y91" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z91" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA91" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB91" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC91" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD91" s="9" t="s">
         <v>247</v>
@@ -29787,34 +29790,34 @@
         <v>2404</v>
       </c>
       <c r="T92" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U92" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V92" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W92" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X92" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y92" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z92" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA92" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB92" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC92" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD92" s="9" t="s">
         <v>234</v>
@@ -29939,34 +29942,34 @@
         <v>2405</v>
       </c>
       <c r="T93" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U93" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V93" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W93" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X93" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y93" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z93" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA93" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB93" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC93" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD93" s="9" t="s">
         <v>248</v>
@@ -30091,34 +30094,34 @@
         <v>2406</v>
       </c>
       <c r="T94" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U94" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V94" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W94" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X94" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y94" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z94" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA94" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB94" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC94" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD94" s="7">
         <v>5</v>
@@ -30243,34 +30246,34 @@
         <v>2407</v>
       </c>
       <c r="T95" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U95" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V95" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W95" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X95" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y95" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z95" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA95" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB95" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC95" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD95" s="8" t="s">
         <v>234</v>
@@ -30395,34 +30398,34 @@
         <v>2408</v>
       </c>
       <c r="T96" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U96" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V96" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W96" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X96" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y96" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z96" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA96" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB96" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC96" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD96" s="9" t="s">
         <v>248</v>
@@ -30547,34 +30550,34 @@
         <v>2409</v>
       </c>
       <c r="T97" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U97" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V97" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W97" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X97" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y97" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z97" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA97" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB97" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC97" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD97" s="8" t="s">
         <v>232</v>
@@ -30699,34 +30702,34 @@
         <v>2410</v>
       </c>
       <c r="T98" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U98" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V98" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W98" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X98" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y98" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z98" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA98" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB98" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC98" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD98" s="7">
         <v>3</v>
@@ -30851,34 +30854,34 @@
         <v>2411</v>
       </c>
       <c r="T99" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U99" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V99" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W99" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X99" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y99" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z99" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA99" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB99" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC99" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD99" s="7">
         <v>3</v>
@@ -31003,34 +31006,34 @@
         <v>2412</v>
       </c>
       <c r="T100" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U100" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V100" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W100" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X100" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y100" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z100" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA100" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB100" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC100" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD100" s="9" t="s">
         <v>247</v>
@@ -31155,34 +31158,34 @@
         <v>2413</v>
       </c>
       <c r="T101" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U101" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V101" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W101" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X101" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y101" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z101" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA101" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB101" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC101" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD101" s="7">
         <v>2</v>
@@ -31307,34 +31310,34 @@
         <v>2414</v>
       </c>
       <c r="T102" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U102" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V102" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W102" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X102" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y102" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z102" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA102" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB102" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC102" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD102" s="9" t="s">
         <v>269</v>
@@ -31477,16 +31480,16 @@
         <v>2483</v>
       </c>
       <c r="Z103" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA103" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB103" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC103" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD103" s="9" t="s">
         <v>232</v>
@@ -31611,34 +31614,34 @@
         <v>2416</v>
       </c>
       <c r="T104" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U104" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V104" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W104" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X104" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y104" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z104" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA104" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB104" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC104" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD104" s="9" t="s">
         <v>247</v>
@@ -31763,10 +31766,10 @@
         <v>2417</v>
       </c>
       <c r="T105" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U105" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V105" s="8" t="s">
         <v>2461</v>
@@ -31787,10 +31790,10 @@
         <v>2466</v>
       </c>
       <c r="AB105" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC105" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD105" s="9" t="s">
         <v>247</v>
@@ -31915,34 +31918,34 @@
         <v>2418</v>
       </c>
       <c r="T106" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U106" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V106" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W106" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X106" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y106" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z106" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA106" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB106" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC106" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD106" s="9" t="s">
         <v>268</v>
@@ -32067,34 +32070,34 @@
         <v>2419</v>
       </c>
       <c r="T107" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U107" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V107" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W107" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X107" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y107" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z107" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA107" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB107" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC107" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD107" s="8" t="s">
         <v>248</v>
@@ -32219,34 +32222,34 @@
         <v>2420</v>
       </c>
       <c r="T108" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U108" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V108" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W108" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X108" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y108" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z108" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA108" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB108" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC108" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD108" s="8">
         <v>3</v>
@@ -32371,34 +32374,34 @@
         <v>2421</v>
       </c>
       <c r="T109" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U109" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V109" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W109" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X109" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y109" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z109" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA109" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB109" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC109" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD109" s="9" t="s">
         <v>235</v>
@@ -32529,28 +32532,28 @@
         <v>2489</v>
       </c>
       <c r="V110" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W110" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X110" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y110" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z110" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA110" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB110" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC110" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD110" s="9" t="s">
         <v>235</v>
@@ -32675,34 +32678,34 @@
         <v>2423</v>
       </c>
       <c r="T111" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U111" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V111" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W111" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X111" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y111" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z111" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA111" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB111" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC111" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD111" s="5" t="s">
         <v>247</v>
@@ -32827,34 +32830,34 @@
         <v>2424</v>
       </c>
       <c r="T112" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U112" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V112" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W112" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X112" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y112" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z112" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA112" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB112" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC112" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD112" s="9" t="s">
         <v>268</v>
@@ -32979,34 +32982,34 @@
         <v>2425</v>
       </c>
       <c r="T113" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U113" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V113" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W113" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X113" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y113" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z113" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA113" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB113" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC113" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD113" s="9" t="s">
         <v>233</v>
@@ -33131,34 +33134,34 @@
         <v>2426</v>
       </c>
       <c r="T114" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U114" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V114" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W114" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X114" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y114" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z114" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA114" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB114" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC114" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD114" s="9" t="s">
         <v>269</v>
@@ -33283,34 +33286,34 @@
         <v>2427</v>
       </c>
       <c r="T115" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U115" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V115" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W115" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X115" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y115" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z115" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA115" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB115" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC115" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD115" s="9" t="s">
         <v>258</v>
@@ -33435,34 +33438,34 @@
         <v>2428</v>
       </c>
       <c r="T116" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U116" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V116" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W116" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X116" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y116" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z116" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA116" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB116" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC116" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD116" s="7" t="s">
         <v>248</v>
@@ -33587,34 +33590,34 @@
         <v>2429</v>
       </c>
       <c r="T117" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U117" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V117" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W117" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X117" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y117" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z117" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA117" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB117" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC117" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD117" s="7" t="s">
         <v>235</v>
@@ -33739,34 +33742,34 @@
         <v>2430</v>
       </c>
       <c r="T118" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U118" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V118" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W118" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X118" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y118" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z118" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA118" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB118" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC118" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD118" s="7" t="s">
         <v>248</v>
@@ -33891,34 +33894,34 @@
         <v>2431</v>
       </c>
       <c r="T119" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U119" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V119" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W119" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X119" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y119" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z119" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA119" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB119" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC119" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD119" s="7" t="s">
         <v>248</v>
@@ -34043,34 +34046,34 @@
         <v>2432</v>
       </c>
       <c r="T120" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U120" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V120" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W120" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X120" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y120" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z120" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA120" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB120" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC120" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD120" s="9" t="s">
         <v>248</v>
@@ -34195,34 +34198,34 @@
         <v>2433</v>
       </c>
       <c r="T121" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U121" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V121" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W121" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X121" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y121" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z121" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA121" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB121" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC121" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD121" s="9" t="s">
         <v>269</v>
@@ -34347,34 +34350,34 @@
         <v>2434</v>
       </c>
       <c r="T122" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U122" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V122" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W122" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X122" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y122" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z122" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA122" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB122" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC122" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD122" s="7" t="s">
         <v>248</v>
@@ -34499,34 +34502,34 @@
         <v>2435</v>
       </c>
       <c r="T123" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U123" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V123" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W123" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X123" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y123" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z123" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA123" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB123" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC123" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD123" s="8" t="s">
         <v>239</v>
@@ -34651,34 +34654,34 @@
         <v>2436</v>
       </c>
       <c r="T124" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U124" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V124" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W124" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X124" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y124" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z124" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA124" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB124" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC124" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD124" s="9" t="s">
         <v>235</v>
@@ -34809,28 +34812,28 @@
         <v>2492</v>
       </c>
       <c r="V125" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W125" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X125" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y125" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z125" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA125" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB125" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC125" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD125" s="9" t="s">
         <v>233</v>
@@ -34955,34 +34958,34 @@
         <v>2438</v>
       </c>
       <c r="T126" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U126" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V126" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W126" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X126" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y126" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z126" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA126" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB126" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC126" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD126" s="7" t="s">
         <v>239</v>
@@ -35107,34 +35110,34 @@
         <v>2439</v>
       </c>
       <c r="T127" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U127" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V127" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W127" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X127" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y127" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z127" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA127" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB127" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC127" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD127" s="7" t="s">
         <v>234</v>
@@ -35259,34 +35262,34 @@
         <v>2440</v>
       </c>
       <c r="T128" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U128" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V128" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W128" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X128" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y128" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z128" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA128" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB128" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC128" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD128" s="5" t="s">
         <v>239</v>
@@ -35411,34 +35414,34 @@
         <v>2441</v>
       </c>
       <c r="T129" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="U129" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="V129" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="W129" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="X129" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Y129" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="Z129" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AA129" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AB129" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AC129" s="8" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="AD129" s="9" t="s">
         <v>248</v>
@@ -35596,19 +35599,19 @@
         <v>56</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -35634,19 +35637,19 @@
         <v>630</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -35672,19 +35675,19 @@
         <v>791</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -35710,19 +35713,19 @@
         <v>990</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -35748,19 +35751,19 @@
         <v>996</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -35786,19 +35789,19 @@
         <v>1002</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -35824,19 +35827,19 @@
         <v>731</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -35862,19 +35865,19 @@
         <v>1008</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -35900,19 +35903,19 @@
         <v>1014</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -35938,19 +35941,19 @@
         <v>797</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -35976,19 +35979,19 @@
         <v>1020</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -36014,19 +36017,19 @@
         <v>62</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -36052,19 +36055,19 @@
         <v>1026</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -36090,19 +36093,19 @@
         <v>1032</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -36128,19 +36131,19 @@
         <v>1038</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -36166,19 +36169,19 @@
         <v>984</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -36204,19 +36207,19 @@
         <v>803</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -36242,19 +36245,19 @@
         <v>880</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -36280,19 +36283,19 @@
         <v>809</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -36318,19 +36321,19 @@
         <v>636</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -36356,19 +36359,19 @@
         <v>1212</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -36394,19 +36397,19 @@
         <v>886</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -36432,19 +36435,19 @@
         <v>737</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -36470,19 +36473,19 @@
         <v>68</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -36508,19 +36511,19 @@
         <v>73</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -36546,19 +36549,19 @@
         <v>1219</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -36584,19 +36587,19 @@
         <v>1044</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -36622,19 +36625,19 @@
         <v>1050</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -36660,19 +36663,19 @@
         <v>892</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -36698,19 +36701,19 @@
         <v>898</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -36736,19 +36739,19 @@
         <v>79</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="33" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -36774,19 +36777,19 @@
         <v>743</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="34" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -36812,19 +36815,19 @@
         <v>1056</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="35" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -36850,19 +36853,19 @@
         <v>815</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="36" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -36888,19 +36891,19 @@
         <v>86</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="37" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -36926,19 +36929,19 @@
         <v>749</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -36964,19 +36967,19 @@
         <v>92</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="39" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -37002,19 +37005,19 @@
         <v>642</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="40" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -37040,19 +37043,19 @@
         <v>755</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="41" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -37078,19 +37081,19 @@
         <v>761</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="42" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -37116,19 +37119,19 @@
         <v>821</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="43" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -37157,16 +37160,16 @@
         <v>2487</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="44" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -37192,19 +37195,19 @@
         <v>1068</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="45" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -37230,19 +37233,19 @@
         <v>827</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="46" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -37268,19 +37271,19 @@
         <v>833</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="47" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -37306,19 +37309,19 @@
         <v>98</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="48" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -37344,19 +37347,19 @@
         <v>904</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="49" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -37382,19 +37385,19 @@
         <v>839</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="50" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -37420,19 +37423,19 @@
         <v>1074</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="51" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -37458,19 +37461,19 @@
         <v>648</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="52" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -37496,19 +37499,19 @@
         <v>910</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="53" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -37534,19 +37537,19 @@
         <v>654</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="54" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -37572,19 +37575,19 @@
         <v>104</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="55" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -37610,19 +37613,19 @@
         <v>660</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="56" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -37648,19 +37651,19 @@
         <v>666</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="57" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -37686,19 +37689,19 @@
         <v>672</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="58" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -37724,19 +37727,19 @@
         <v>1080</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="59" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -37762,19 +37765,19 @@
         <v>845</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="60" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -37800,19 +37803,19 @@
         <v>916</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="61" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -37838,19 +37841,19 @@
         <v>922</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="62" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -37876,19 +37879,19 @@
         <v>1086</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="63" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -37914,19 +37917,19 @@
         <v>851</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="64" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -37952,19 +37955,19 @@
         <v>678</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="65" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -37990,19 +37993,19 @@
         <v>1092</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="66" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -38028,19 +38031,19 @@
         <v>110</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="67" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -38066,19 +38069,19 @@
         <v>208</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="68" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -38104,19 +38107,19 @@
         <v>767</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="69" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -38142,19 +38145,19 @@
         <v>1249</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="70" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -38180,19 +38183,19 @@
         <v>684</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="71" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -38218,19 +38221,19 @@
         <v>928</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="72" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -38256,19 +38259,19 @@
         <v>1098</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="73" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -38294,19 +38297,19 @@
         <v>856</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="74" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -38332,19 +38335,19 @@
         <v>2479</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="75" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -38370,19 +38373,19 @@
         <v>690</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="76" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -38408,19 +38411,19 @@
         <v>1104</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="77" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -38446,19 +38449,19 @@
         <v>936</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="78" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -38484,19 +38487,19 @@
         <v>1110</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="79" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -38522,19 +38525,19 @@
         <v>942</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="80" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -38560,19 +38563,19 @@
         <v>696</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="81" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -38598,19 +38601,19 @@
         <v>773</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="82" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -38636,19 +38639,19 @@
         <v>1241</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="83" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -38674,19 +38677,19 @@
         <v>202</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="84" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -38712,19 +38715,19 @@
         <v>196</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="85" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -38750,19 +38753,19 @@
         <v>190</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L85" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="86" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -38788,19 +38791,19 @@
         <v>1116</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L86" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="87" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -38826,19 +38829,19 @@
         <v>1122</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L87" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="88" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -38864,19 +38867,19 @@
         <v>779</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J88" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K88" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L88" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="89" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -38902,19 +38905,19 @@
         <v>978</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L89" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="90" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -38940,19 +38943,19 @@
         <v>862</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K90" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L90" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="91" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -38978,19 +38981,19 @@
         <v>1127</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J91" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K91" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L91" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="92" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -39016,19 +39019,19 @@
         <v>948</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L92" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="93" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -39054,19 +39057,19 @@
         <v>954</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K93" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L93" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="94" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -39092,19 +39095,19 @@
         <v>184</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L94" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="95" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -39130,19 +39133,19 @@
         <v>701</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J95" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K95" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L95" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="96" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -39168,19 +39171,19 @@
         <v>960</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K96" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L96" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="97" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -39206,19 +39209,19 @@
         <v>707</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I97" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J97" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K97" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L97" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="98" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -39244,19 +39247,19 @@
         <v>178</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I98" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J98" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K98" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L98" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="99" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -39282,19 +39285,19 @@
         <v>172</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J99" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L99" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="100" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -39320,19 +39323,19 @@
         <v>1133</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I100" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J100" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K100" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L100" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="101" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -39358,19 +39361,19 @@
         <v>166</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J101" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K101" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L101" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="102" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -39396,19 +39399,19 @@
         <v>1139</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J102" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K102" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L102" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="103" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -39443,10 +39446,10 @@
         <v>963</v>
       </c>
       <c r="K103" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L103" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="104" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -39472,19 +39475,19 @@
         <v>785</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I104" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J104" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K104" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L104" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="105" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -39510,7 +39513,7 @@
         <v>1145</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I105" s="3" t="s">
         <v>2467</v>
@@ -39548,19 +39551,19 @@
         <v>1151</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I106" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J106" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K106" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L106" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="107" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -39586,19 +39589,19 @@
         <v>713</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I107" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J107" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K107" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L107" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="108" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -39624,19 +39627,19 @@
         <v>719</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I108" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J108" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K108" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L108" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="109" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -39662,19 +39665,19 @@
         <v>1157</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I109" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J109" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K109" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L109" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="110" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -39703,16 +39706,16 @@
         <v>2490</v>
       </c>
       <c r="I110" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J110" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K110" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L110" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="111" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -39738,19 +39741,19 @@
         <v>1235</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I111" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J111" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K111" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L111" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="112" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -39776,19 +39779,19 @@
         <v>1169</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I112" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J112" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K112" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L112" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="113" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -39814,19 +39817,19 @@
         <v>1175</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I113" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J113" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K113" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L113" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="114" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -39852,19 +39855,19 @@
         <v>868</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I114" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J114" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K114" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L114" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="115" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -39890,19 +39893,19 @@
         <v>874</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I115" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J115" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K115" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L115" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="116" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -39928,19 +39931,19 @@
         <v>160</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I116" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J116" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K116" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L116" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="117" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -39966,19 +39969,19 @@
         <v>154</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I117" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J117" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K117" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L117" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="118" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -40004,19 +40007,19 @@
         <v>148</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I118" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J118" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K118" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L118" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="119" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -40042,19 +40045,19 @@
         <v>142</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I119" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J119" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K119" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L119" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="120" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -40080,19 +40083,19 @@
         <v>972</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I120" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J120" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K120" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L120" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="121" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -40118,19 +40121,19 @@
         <v>1181</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I121" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J121" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K121" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L121" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="122" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -40156,19 +40159,19 @@
         <v>136</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I122" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J122" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K122" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L122" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="123" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -40194,19 +40197,19 @@
         <v>725</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I123" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J123" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K123" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L123" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="124" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -40232,19 +40235,19 @@
         <v>1187</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I124" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J124" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K124" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L124" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="125" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -40273,16 +40276,16 @@
         <v>2493</v>
       </c>
       <c r="I125" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J125" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K125" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L125" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="126" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -40308,19 +40311,19 @@
         <v>130</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I126" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J126" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K126" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L126" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="127" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -40346,19 +40349,19 @@
         <v>124</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I127" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J127" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K127" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L127" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="128" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -40384,19 +40387,19 @@
         <v>1226</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I128" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J128" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K128" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L128" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="129" spans="1:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -40422,19 +40425,19 @@
         <v>1199</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="I129" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="J129" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="K129" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
       <c r="L129" s="2" t="s">
-        <v>2451</v>
+        <v>2494</v>
       </c>
     </row>
   </sheetData>
